--- a/DADOS/parcerias_lat_long.xlsx
+++ b/DADOS/parcerias_lat_long.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://spparceriassa-my.sharepoint.com/personal/vitorio_aflalo_spparcerias_com_br/Documents/Área de Trabalho/PROJETOS/DASHBOARDS SOCIAIS/INDICADORES BASE/VERSÃO 2/MAPA-SHINY/DADOS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="514" documentId="11_5C3D73BED3F05465B3F93711595ED87656CFE358" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EA754C28-9766-4F0F-8BE9-A4A175159C4F}"/>
+  <xr:revisionPtr revIDLastSave="538" documentId="11_5C3D73BED3F05465B3F93711595ED87656CFE358" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EA29B242-1D04-4747-A4F9-18C4C817AF3C}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$K$108</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$K$106</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="867" uniqueCount="331">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="859" uniqueCount="327">
   <si>
     <t>geometry</t>
   </si>
@@ -76,9 +76,6 @@
     <t>Baixo do Viaduto Lapa</t>
   </si>
   <si>
-    <t>Baixo do Viaduto Pompéia</t>
-  </si>
-  <si>
     <t>Cemitério Vila Formosa I</t>
   </si>
   <si>
@@ -190,9 +187,6 @@
     <t>Terminal Santo Amaro</t>
   </si>
   <si>
-    <t>Terminal Varginha</t>
-  </si>
-  <si>
     <t>CEU Imperador</t>
   </si>
   <si>
@@ -334,9 +328,6 @@
     <t>Parceria público-privada (PPP)</t>
   </si>
   <si>
-    <t>Concessão</t>
-  </si>
-  <si>
     <t>Termo de permissão de uso (TPU)</t>
   </si>
   <si>
@@ -385,9 +376,6 @@
     <t>https://www.prefeitura.sp.gov.br/cidade/secretarias/governo/desestatizacao_projetos/baixos_viadutos/viaduto_lapa/index.php?p=342074</t>
   </si>
   <si>
-    <t>TERMO DE PERMISSÃO DE USO Nº 001/SUB-LA/2020</t>
-  </si>
-  <si>
     <t>SMC</t>
   </si>
   <si>
@@ -589,12 +577,6 @@
     <t>https://www.prefeitura.sp.gov.br/cidade/secretarias/governo/desestatizacao_projetos/pacaembu/index.php?p=341575</t>
   </si>
   <si>
-    <t>Parada 14 Bis</t>
-  </si>
-  <si>
-    <t>Parada - Bloco Sul</t>
-  </si>
-  <si>
     <t>SPE SÃO PAULO SUL S.A.</t>
   </si>
   <si>
@@ -667,9 +649,6 @@
     <t>Terminal Estação Varginha</t>
   </si>
   <si>
-    <t>Terminais Hidroviários (Bloco Sul)</t>
-  </si>
-  <si>
     <t>Terminal São Mateus</t>
   </si>
   <si>
@@ -691,12 +670,6 @@
     <t>ppp_area m2</t>
   </si>
   <si>
-    <t>ADRIANA ALVES DO NASCIMENTO 28869014827</t>
-  </si>
-  <si>
-    <t>https://prefeitura.sp.gov.br/web/desestatizacao_projetos/baixos_viadutos</t>
-  </si>
-  <si>
     <t>ppp_link</t>
   </si>
   <si>
@@ -706,9 +679,6 @@
     <t>POINT(-23.518492511914697 -46.699990927278954)</t>
   </si>
   <si>
-    <t>POINT(-23.533082614245753 -46.68697761408343)</t>
-  </si>
-  <si>
     <t>POINT (-23.5474534 -46.6420769)</t>
   </si>
   <si>
@@ -1006,9 +976,6 @@
     <t>POINT(-23.61437377036193 -46.50088174756313)</t>
   </si>
   <si>
-    <t>POINT(-23.766784504881343 -46.7162363574993)</t>
-  </si>
-  <si>
     <t>POINT(-23.558212286241517 -46.52269470154135)</t>
   </si>
   <si>
@@ -1016,24 +983,37 @@
   </si>
   <si>
     <t>POINT(-23.54462393536879 -46.63620587284597)</t>
+  </si>
+  <si>
+    <t>Concessão Comum</t>
+  </si>
+  <si>
+    <t>Parada 14 Bis (Sistema de Elevadores)</t>
+  </si>
+  <si>
+    <t>Esplanada da Liberdade</t>
+  </si>
+  <si>
+    <t>Consórcio Parque Liberdade</t>
+  </si>
+  <si>
+    <t>CONTRATO Nº 008/SP-REGULA/2026</t>
+  </si>
+  <si>
+    <t>https://prefeitura.sp.gov.br/web/desestatizacao_projetos/w/esplanada_liberdade/342546</t>
+  </si>
+  <si>
+    <t>POINT(-23.555845969941895 -46.63430347541247)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1077,18 +1057,15 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1389,7 +1366,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K108"/>
+  <dimension ref="A1:K107"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="44.109375" style="2" bestFit="1" customWidth="1"/>
@@ -1407,72 +1384,72 @@
   <sheetData>
     <row r="1" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>110</v>
-      </c>
       <c r="K1" s="1" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>103</v>
+        <v>320</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F2" s="1">
         <v>920.28</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="H2" s="1">
         <v>2021</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="J2" s="1">
         <v>5373000</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1480,13 +1457,13 @@
         <v>16</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>103</v>
+        <v>320</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>16</v>
@@ -1495,45 +1472,45 @@
         <v>350.39</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="H3" s="1">
         <v>2022</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="J3" s="1">
         <v>5193000</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>17</v>
+        <v>69</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>17</v>
+        <v>118</v>
       </c>
       <c r="F4" s="1">
-        <v>337.94</v>
+        <v>208.49</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>222</v>
+        <v>119</v>
       </c>
       <c r="H4" s="1">
-        <v>2020</v>
+        <v>2024</v>
       </c>
       <c r="I4" s="1" t="s">
         <v>120</v>
@@ -1541,98 +1518,98 @@
       <c r="J4" s="1">
         <v>0</v>
       </c>
-      <c r="K4" s="3" t="s">
-        <v>223</v>
+      <c r="K4" s="1" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>121</v>
+        <v>88</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>104</v>
+        <v>320</v>
       </c>
       <c r="E5" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F5" s="1">
+        <v>385883.68</v>
+      </c>
+      <c r="G5" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="F5" s="1">
-        <v>208.49</v>
-      </c>
-      <c r="G5" s="1" t="s">
+      <c r="H5" s="1">
+        <v>2025</v>
+      </c>
+      <c r="I5" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="H5" s="1">
-        <v>2024</v>
-      </c>
-      <c r="I5" s="1" t="s">
+      <c r="J5" s="1">
+        <v>202000</v>
+      </c>
+      <c r="K5" s="1" t="s">
         <v>124</v>
-      </c>
-      <c r="J5" s="1">
-        <v>0</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>57</v>
+        <v>93</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>90</v>
+        <v>125</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>103</v>
+        <v>320</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>57</v>
+        <v>126</v>
       </c>
       <c r="F6" s="1">
-        <v>385883.68</v>
+        <v>69704.94</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H6" s="1">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="J6" s="1">
-        <v>202000</v>
+        <v>6492000</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>95</v>
+        <v>28</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>103</v>
+        <v>320</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>130</v>
       </c>
       <c r="F7" s="1">
-        <v>69704.94</v>
+        <v>14387.63</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>131</v>
@@ -1644,205 +1621,205 @@
         <v>132</v>
       </c>
       <c r="J7" s="1">
-        <v>6492000</v>
+        <v>2641000</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>103</v>
+        <v>320</v>
       </c>
       <c r="E8" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="F8" s="1">
+        <v>105796.42</v>
+      </c>
+      <c r="G8" s="1" t="s">
         <v>134</v>
-      </c>
-      <c r="F8" s="1">
-        <v>14387.63</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>135</v>
       </c>
       <c r="H8" s="1">
         <v>2022</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="J8" s="1">
-        <v>2641000</v>
+        <v>6716000</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>103</v>
+        <v>320</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="F9" s="1">
-        <v>105796.42</v>
+        <v>16300.78</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="H9" s="1">
         <v>2022</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="J9" s="1">
-        <v>6716000</v>
+        <v>1821000</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>103</v>
+        <v>320</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="F10" s="1">
-        <v>16300.78</v>
+        <v>170193.09</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="H10" s="1">
         <v>2022</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="J10" s="1">
-        <v>1821000</v>
+        <v>11890000</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>103</v>
+        <v>320</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="F11" s="1">
-        <v>170193.09</v>
+        <v>134592.34</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="H11" s="1">
         <v>2022</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="J11" s="1">
-        <v>11890000</v>
+        <v>20733000</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>103</v>
+        <v>320</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="F12" s="1">
-        <v>134592.34</v>
+        <v>63695.77</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="H12" s="1">
         <v>2022</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="J12" s="1">
-        <v>20733000</v>
+        <v>9729000</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>103</v>
+        <v>320</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>130</v>
       </c>
       <c r="F13" s="1">
-        <v>63695.77</v>
+        <v>111430.69</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>131</v>
@@ -1854,701 +1831,701 @@
         <v>132</v>
       </c>
       <c r="J13" s="1">
-        <v>9729000</v>
+        <v>17581000</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>103</v>
+        <v>320</v>
       </c>
       <c r="E14" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="F14" s="1">
+        <v>5347.15</v>
+      </c>
+      <c r="G14" s="1" t="s">
         <v>134</v>
-      </c>
-      <c r="F14" s="1">
-        <v>111430.69</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>135</v>
       </c>
       <c r="H14" s="1">
         <v>2022</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="J14" s="1">
-        <v>17581000</v>
+        <v>1559000</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>103</v>
+        <v>320</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="F15" s="1">
-        <v>5347.15</v>
+        <v>40918.699999999997</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="H15" s="1">
         <v>2022</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="J15" s="1">
-        <v>1559000</v>
+        <v>4512000</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>103</v>
+        <v>320</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="F16" s="1">
-        <v>40918.699999999997</v>
+        <v>30169.58</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="H16" s="1">
         <v>2022</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="J16" s="1">
-        <v>4512000</v>
+        <v>3007000</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>103</v>
+        <v>320</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="F17" s="1">
-        <v>30169.58</v>
+        <v>66992.95</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>141</v>
+        <v>127</v>
       </c>
       <c r="H17" s="1">
         <v>2022</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="J17" s="1">
-        <v>3007000</v>
+        <v>6032000</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>103</v>
+        <v>320</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="F18" s="1">
-        <v>66992.95</v>
+        <v>222160.66</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="H18" s="1">
         <v>2022</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="J18" s="1">
-        <v>6032000</v>
+        <v>11641000</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>103</v>
+        <v>320</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="F19" s="1">
-        <v>222160.66</v>
+        <v>110424.55</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="H19" s="1">
         <v>2022</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="J19" s="1">
-        <v>11641000</v>
+        <v>17028000</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>36</v>
+        <v>102</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>103</v>
+        <v>320</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="F20" s="1">
-        <v>110424.55</v>
+        <v>52858.57</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="H20" s="1">
         <v>2022</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="J20" s="1">
-        <v>17028000</v>
+        <v>10717000</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>105</v>
+        <v>22</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>103</v>
+        <v>320</v>
       </c>
       <c r="E21" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="F21" s="1">
+        <v>225437.73</v>
+      </c>
+      <c r="G21" s="1" t="s">
         <v>137</v>
-      </c>
-      <c r="F21" s="1">
-        <v>52858.57</v>
-      </c>
-      <c r="G21" s="1" t="s">
-        <v>138</v>
       </c>
       <c r="H21" s="1">
         <v>2022</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="J21" s="1">
-        <v>10717000</v>
+        <v>38478000</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>103</v>
+        <v>320</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="F22" s="1">
-        <v>225437.73</v>
+        <v>235772.55</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="H22" s="1">
         <v>2022</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="J22" s="1">
-        <v>38478000</v>
+        <v>39984000</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>103</v>
+        <v>320</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="F23" s="1">
-        <v>235772.55</v>
+        <v>104764.86</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H23" s="1">
         <v>2022</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="J23" s="1">
-        <v>39984000</v>
+        <v>6253000</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>247</v>
+        <v>238</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>103</v>
+        <v>320</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="F24" s="1">
-        <v>104764.86</v>
+        <v>235074.91</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="H24" s="1">
         <v>2022</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="J24" s="1">
-        <v>6253000</v>
+        <v>41655000</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>248</v>
+        <v>239</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>103</v>
+        <v>320</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="F25" s="1">
-        <v>235074.91</v>
+        <v>314511.48</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="H25" s="1">
         <v>2022</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="J25" s="1">
-        <v>41655000</v>
+        <v>57984000</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>103</v>
+        <v>320</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="F26" s="1">
-        <v>314511.48</v>
+        <v>360539.76</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="H26" s="1">
         <v>2022</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="J26" s="1">
-        <v>57984000</v>
+        <v>73606000</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="27" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>39</v>
+        <v>94</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>103</v>
+        <v>320</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="F27" s="1">
-        <v>360539.76</v>
+        <v>227597.77</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="H27" s="1">
         <v>2022</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="J27" s="1">
-        <v>73606000</v>
+        <v>34889000</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="28" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>96</v>
+        <v>70</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E28" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="F28" s="1">
+        <v>46.11</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="H28" s="1">
+        <v>2024</v>
+      </c>
+      <c r="I28" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="F28" s="1">
-        <v>227597.77</v>
-      </c>
-      <c r="G28" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="H28" s="1">
-        <v>2022</v>
-      </c>
-      <c r="I28" s="1" t="s">
-        <v>142</v>
-      </c>
       <c r="J28" s="1">
-        <v>34889000</v>
+        <v>0</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
     </row>
     <row r="29" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>72</v>
+        <v>108</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>252</v>
+        <v>243</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="F29" s="1">
-        <v>46.11</v>
+        <v>68.8</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="H29" s="1">
         <v>2024</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="J29" s="1">
         <v>0</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
     </row>
     <row r="30" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="F30" s="1">
-        <v>68.8</v>
+        <v>88.75</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="H30" s="1">
         <v>2024</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="J30" s="1">
         <v>0</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
     </row>
     <row r="31" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>112</v>
+        <v>71</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="F31" s="1">
-        <v>88.75</v>
+        <v>83.07</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="H31" s="1">
         <v>2024</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="J31" s="1">
         <v>0</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
     </row>
     <row r="32" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>121</v>
+        <v>145</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>122</v>
+        <v>56</v>
       </c>
       <c r="F32" s="1">
-        <v>83.07</v>
+        <v>5387</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H32" s="1">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J32" s="1">
         <v>0</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>125</v>
+        <v>148</v>
       </c>
     </row>
     <row r="33" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="C33" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="E33" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="D33" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>58</v>
-      </c>
       <c r="F33" s="1">
-        <v>5387</v>
+        <v>10587.39</v>
       </c>
       <c r="G33" s="1" t="s">
         <v>150</v>
       </c>
       <c r="H33" s="1">
-        <v>2025</v>
+        <v>2021</v>
       </c>
       <c r="I33" s="1" t="s">
         <v>151</v>
@@ -2562,107 +2539,107 @@
     </row>
     <row r="34" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>59</v>
+        <v>153</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F34" s="1">
-        <v>10587.39</v>
+        <v>12708.97</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H34" s="1">
-        <v>2021</v>
+        <v>2024</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J34" s="1">
-        <v>0</v>
+        <v>80660000</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="35" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
-        <v>157</v>
+        <v>58</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>257</v>
+        <v>248</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="F35" s="1">
-        <v>12708.97</v>
+        <v>10587.39</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="H35" s="1">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="J35" s="1">
-        <v>80660000</v>
+        <v>0</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
     </row>
     <row r="36" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="F36" s="1">
-        <v>10587.39</v>
+        <v>19541.29</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="H36" s="1">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="J36" s="1">
-        <v>0</v>
+        <v>76009</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
     </row>
     <row r="37" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -2670,372 +2647,372 @@
         <v>42</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="F37" s="1">
-        <v>19541.29</v>
+        <v>13590.25</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="H37" s="1">
         <v>2022</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="J37" s="1">
-        <v>76009</v>
+        <v>96994</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
     </row>
     <row r="38" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="E38" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="F38" s="1">
+        <v>11636</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="H38" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I38" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="F38" s="1">
-        <v>13590.25</v>
-      </c>
-      <c r="G38" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="H38" s="1">
-        <v>2022</v>
-      </c>
-      <c r="I38" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="J38" s="1">
-        <v>96994</v>
+        <v>0</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
     </row>
     <row r="39" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>261</v>
+        <v>252</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="F39" s="1">
-        <v>11636</v>
+        <v>19578.52</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="H39" s="1">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="J39" s="1">
-        <v>0</v>
+        <v>99564</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
     </row>
     <row r="40" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>44</v>
+        <v>72</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>262</v>
+        <v>253</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
       <c r="F40" s="1">
-        <v>19578.52</v>
+        <v>11554.06</v>
       </c>
       <c r="G40" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="H40" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I40" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="H40" s="1">
-        <v>2022</v>
-      </c>
-      <c r="I40" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="J40" s="1">
-        <v>99564</v>
+        <v>0</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
     </row>
     <row r="41" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="F41" s="1">
-        <v>11554.06</v>
+        <v>15287.47</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="H41" s="1">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="J41" s="1">
-        <v>0</v>
+        <v>53300</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
     </row>
     <row r="42" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="F42" s="1">
-        <v>15287.47</v>
+        <v>9497.76</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="H42" s="1">
         <v>2022</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="J42" s="1">
-        <v>53300</v>
+        <v>87297</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
     </row>
     <row r="43" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
-        <v>56</v>
+        <v>164</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="F43" s="1">
-        <v>9497.76</v>
+        <v>73046.34</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="H43" s="1">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="J43" s="1">
-        <v>87297</v>
+        <v>84810000</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
     </row>
     <row r="44" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
-        <v>168</v>
+        <v>60</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>266</v>
+        <v>257</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="F44" s="1">
-        <v>73046.34</v>
+        <v>13651.91</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="H44" s="1">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="J44" s="1">
-        <v>84810000</v>
+        <v>0</v>
       </c>
       <c r="K44" s="1" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
     </row>
     <row r="45" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
-        <v>62</v>
+        <v>165</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>267</v>
+        <v>258</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F45" s="1">
-        <v>13651.91</v>
+        <v>13497.6</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H45" s="1">
-        <v>2021</v>
+        <v>2024</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="J45" s="1">
-        <v>0</v>
+        <v>80670000</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="46" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
-        <v>169</v>
+        <v>73</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>268</v>
+        <v>259</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="F46" s="1">
-        <v>13497.6</v>
+        <v>12662.59</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="H46" s="1">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="J46" s="1">
-        <v>80670000</v>
+        <v>0</v>
       </c>
       <c r="K46" s="1" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
     </row>
     <row r="47" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>269</v>
+        <v>260</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="F47" s="1">
-        <v>12662.59</v>
+        <v>12341.94</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="H47" s="1">
         <v>2021</v>
@@ -3047,457 +3024,457 @@
         <v>0</v>
       </c>
       <c r="K47" s="1" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="48" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="F48" s="1">
-        <v>12341.94</v>
+        <v>13653</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="H48" s="1">
         <v>2021</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="J48" s="1">
         <v>0</v>
       </c>
       <c r="K48" s="1" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="49" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
-        <v>64</v>
+        <v>167</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F49" s="1">
-        <v>13653</v>
+        <v>35656.42</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H49" s="1">
-        <v>2021</v>
+        <v>2024</v>
       </c>
       <c r="I49" s="1" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="J49" s="1">
-        <v>0</v>
+        <v>73310000</v>
       </c>
       <c r="K49" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="50" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
-        <v>171</v>
+        <v>63</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>272</v>
+        <v>263</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="F50" s="1">
-        <v>35656.42</v>
+        <v>9448.6200000000008</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="H50" s="1">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="I50" s="1" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="J50" s="1">
-        <v>73310000</v>
+        <v>0</v>
       </c>
       <c r="K50" s="1" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
     </row>
     <row r="51" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>273</v>
+        <v>264</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="F51" s="1">
-        <v>9448.6200000000008</v>
+        <v>10269</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="H51" s="1">
         <v>2021</v>
       </c>
       <c r="I51" s="1" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="J51" s="1">
         <v>0</v>
       </c>
       <c r="K51" s="1" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="52" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>274</v>
+        <v>265</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="F52" s="1">
-        <v>10269</v>
+        <v>10800</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="H52" s="1">
         <v>2021</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="J52" s="1">
         <v>0</v>
       </c>
       <c r="K52" s="1" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="53" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>275</v>
+        <v>266</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="F53" s="1">
-        <v>10800</v>
+        <v>12124.52</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="H53" s="1">
         <v>2021</v>
       </c>
       <c r="I53" s="1" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="J53" s="1">
         <v>0</v>
       </c>
       <c r="K53" s="1" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="54" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>68</v>
+        <v>168</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F54" s="1">
-        <v>12124.52</v>
+        <v>14876.93</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H54" s="1">
-        <v>2021</v>
+        <v>2024</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J54" s="1">
-        <v>0</v>
+        <v>81590000</v>
       </c>
       <c r="K54" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="55" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F55" s="1">
+        <v>134577.9</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="H55" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I55" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="J55" s="1">
+        <v>66173700</v>
+      </c>
+      <c r="K55" s="1" t="s">
         <v>172</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="E55" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="F55" s="1">
-        <v>14876.93</v>
-      </c>
-      <c r="G55" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="H55" s="1">
-        <v>2024</v>
-      </c>
-      <c r="I55" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="J55" s="1">
-        <v>81590000</v>
-      </c>
-      <c r="K55" s="1" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="56" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>278</v>
+        <v>269</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>173</v>
+        <v>125</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>103</v>
+        <v>320</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>46</v>
+        <v>130</v>
       </c>
       <c r="F56" s="1">
-        <v>134577.9</v>
+        <v>54907.83</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>174</v>
+        <v>131</v>
       </c>
       <c r="H56" s="1">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="I56" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="J56" s="1">
-        <v>66173700</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="J56" s="1"/>
       <c r="K56" s="1" t="s">
-        <v>176</v>
+        <v>129</v>
       </c>
     </row>
     <row r="57" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>279</v>
+        <v>270</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>103</v>
+        <v>320</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>134</v>
+        <v>173</v>
       </c>
       <c r="F57" s="1">
-        <v>54907.83</v>
+        <v>9205.65</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>135</v>
+        <v>174</v>
       </c>
       <c r="H57" s="1">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="I57" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="J57" s="1"/>
+        <v>175</v>
+      </c>
+      <c r="J57" s="1">
+        <v>21342000</v>
+      </c>
       <c r="K57" s="1" t="s">
-        <v>133</v>
+        <v>161</v>
       </c>
     </row>
     <row r="58" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>103</v>
+        <v>320</v>
       </c>
       <c r="E58" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="F58" s="1">
+        <v>4899.92</v>
+      </c>
+      <c r="G58" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="F58" s="1">
-        <v>9205.65</v>
-      </c>
-      <c r="G58" s="1" t="s">
+      <c r="H58" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I58" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="H58" s="1">
-        <v>2019</v>
-      </c>
-      <c r="I58" s="1" t="s">
+      <c r="J58" s="1">
+        <v>16299903</v>
+      </c>
+      <c r="K58" s="1" t="s">
         <v>179</v>
-      </c>
-      <c r="J58" s="1">
-        <v>21342000</v>
-      </c>
-      <c r="K58" s="1" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="59" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>103</v>
+        <v>320</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="F59" s="1">
-        <v>4899.92</v>
+        <v>24229.91</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="H59" s="1">
         <v>2021</v>
       </c>
       <c r="I59" s="1" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="J59" s="1">
-        <v>16299903</v>
+        <v>66853213</v>
       </c>
       <c r="K59" s="1" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
     </row>
     <row r="60" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>32</v>
+        <v>180</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>282</v>
+        <v>273</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>129</v>
+        <v>91</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>103</v>
+        <v>320</v>
       </c>
       <c r="E60" s="1" t="s">
         <v>180</v>
       </c>
       <c r="F60" s="1">
-        <v>24229.91</v>
+        <v>66044.7</v>
       </c>
       <c r="G60" s="1" t="s">
         <v>181</v>
       </c>
       <c r="H60" s="1">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="I60" s="1" t="s">
         <v>182</v>
       </c>
       <c r="J60" s="1">
-        <v>66853213</v>
+        <v>22003400</v>
       </c>
       <c r="K60" s="1" t="s">
         <v>183</v>
@@ -3505,1599 +3482,1599 @@
     </row>
     <row r="61" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="F61" s="1"/>
+      <c r="G61" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="B61" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E61" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="F61" s="1">
-        <v>66044.7</v>
-      </c>
-      <c r="G61" s="1" t="s">
+      <c r="H61" s="1">
+        <v>2026</v>
+      </c>
+      <c r="I61" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="H61" s="1">
-        <v>2019</v>
-      </c>
-      <c r="I61" s="1" t="s">
+      <c r="J61" s="1"/>
+      <c r="K61" s="1" t="s">
         <v>186</v>
-      </c>
-      <c r="J61" s="1">
-        <v>22003400</v>
-      </c>
-      <c r="K61" s="1" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="62" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="F62" s="1">
+        <v>38840.76</v>
+      </c>
+      <c r="G62" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="B62" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="D62" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="E62" s="1" t="s">
+      <c r="H62" s="1">
+        <v>2019</v>
+      </c>
+      <c r="I62" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="F62" s="1"/>
-      <c r="G62" s="1" t="s">
+      <c r="J62" s="1">
+        <v>1500000</v>
+      </c>
+      <c r="K62" s="1" t="s">
         <v>190</v>
-      </c>
-      <c r="H62" s="1">
-        <v>2026</v>
-      </c>
-      <c r="I62" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="J62" s="1"/>
-      <c r="K62" s="1" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="63" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>285</v>
+        <v>276</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>103</v>
+        <v>320</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="F63" s="1">
-        <v>38840.76</v>
+        <v>1122644.73</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="H63" s="1">
         <v>2019</v>
       </c>
       <c r="I63" s="1" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="J63" s="1">
-        <v>1500000</v>
+        <v>91900000</v>
       </c>
       <c r="K63" s="1" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
     </row>
     <row r="64" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
-        <v>6</v>
+        <v>103</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>286</v>
+        <v>277</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>103</v>
+        <v>320</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="F64" s="1">
-        <v>1122644.73</v>
+        <v>15964.59</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="H64" s="1">
         <v>2019</v>
       </c>
       <c r="I64" s="1" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="J64" s="1">
-        <v>91900000</v>
+        <v>1200000</v>
       </c>
       <c r="K64" s="1" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
     </row>
     <row r="65" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
-        <v>106</v>
+        <v>191</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>287</v>
+        <v>278</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>90</v>
+        <v>125</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="E65" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="F65" s="1">
+        <v>337229</v>
+      </c>
+      <c r="G65" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="H65" s="1">
+        <v>2026</v>
+      </c>
+      <c r="I65" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="F65" s="1">
-        <v>15964.59</v>
-      </c>
-      <c r="G65" s="1" t="s">
+      <c r="J65" s="1">
+        <v>717270000</v>
+      </c>
+      <c r="K65" s="1" t="s">
         <v>194</v>
-      </c>
-      <c r="H65" s="1">
-        <v>2019</v>
-      </c>
-      <c r="I65" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="J65" s="1">
-        <v>1200000</v>
-      </c>
-      <c r="K65" s="1" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="66" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
-        <v>197</v>
+        <v>33</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>129</v>
+        <v>88</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>102</v>
+        <v>320</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="F66" s="1">
-        <v>337229</v>
+        <v>22505.08</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="H66" s="1">
-        <v>2026</v>
+        <v>2019</v>
       </c>
       <c r="I66" s="1" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="J66" s="1">
-        <v>717270000</v>
+        <v>700000</v>
       </c>
       <c r="K66" s="1" t="s">
-        <v>200</v>
+        <v>190</v>
       </c>
     </row>
     <row r="67" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
-        <v>34</v>
+        <v>74</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>103</v>
+        <v>320</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="F67" s="1">
-        <v>22505.08</v>
+        <v>34446.080000000002</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="H67" s="1">
         <v>2019</v>
       </c>
       <c r="I67" s="1" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="J67" s="1">
-        <v>700000</v>
+        <v>2400000</v>
       </c>
       <c r="K67" s="1" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
     </row>
     <row r="68" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
-        <v>76</v>
+        <v>34</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>103</v>
+        <v>320</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="F68" s="1">
-        <v>34446.080000000002</v>
+        <v>30063.1</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="H68" s="1">
         <v>2019</v>
       </c>
       <c r="I68" s="1" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="J68" s="1">
-        <v>2400000</v>
+        <v>1600000</v>
       </c>
       <c r="K68" s="1" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
     </row>
     <row r="69" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>103</v>
+        <v>320</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F69" s="1">
-        <v>30063.1</v>
+        <v>5369.34</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="H69" s="1">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="I69" s="1" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="J69" s="1">
-        <v>1600000</v>
+        <v>70185</v>
       </c>
       <c r="K69" s="1" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="70" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>103</v>
+        <v>320</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F70" s="1">
-        <v>5369.34</v>
+        <v>39772.269999999997</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="H70" s="1">
         <v>2022</v>
       </c>
       <c r="I70" s="1" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="J70" s="1">
-        <v>70185</v>
+        <v>806120</v>
       </c>
       <c r="K70" s="1" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
     </row>
     <row r="71" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>103</v>
+        <v>320</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F71" s="1">
-        <v>39772.269999999997</v>
+        <v>11361.75</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="H71" s="1">
         <v>2022</v>
       </c>
       <c r="I71" s="1" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="J71" s="1">
-        <v>806120</v>
+        <v>123695</v>
       </c>
       <c r="K71" s="1" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
     </row>
     <row r="72" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="F72" s="1">
-        <v>11361.75</v>
+        <v>3749.28</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>202</v>
+        <v>184</v>
       </c>
       <c r="H72" s="1">
         <v>2022</v>
       </c>
       <c r="I72" s="1" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="J72" s="1">
-        <v>123695</v>
+        <v>3990000</v>
       </c>
       <c r="K72" s="1" t="s">
-        <v>204</v>
+        <v>186</v>
       </c>
     </row>
     <row r="73" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="F73" s="1">
-        <v>3749.28</v>
+        <v>10022</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="H73" s="1">
         <v>2022</v>
       </c>
       <c r="I73" s="1" t="s">
-        <v>191</v>
+        <v>202</v>
       </c>
       <c r="J73" s="1">
-        <v>3990000</v>
+        <v>3637000</v>
       </c>
       <c r="K73" s="1" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
     </row>
     <row r="74" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
-        <v>47</v>
+        <v>76</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E74" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="F74" s="1">
+        <v>10936</v>
+      </c>
+      <c r="G74" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="H74" s="1">
+        <v>2025</v>
+      </c>
+      <c r="I74" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="J74" s="1">
+        <v>9545000</v>
+      </c>
+      <c r="K74" s="1" t="s">
         <v>206</v>
-      </c>
-      <c r="F74" s="1">
-        <v>10022</v>
-      </c>
-      <c r="G74" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="H74" s="1">
-        <v>2022</v>
-      </c>
-      <c r="I74" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="J74" s="1">
-        <v>3637000</v>
-      </c>
-      <c r="K74" s="1" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="75" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="F75" s="1">
-        <v>10936</v>
+        <v>6213</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="H75" s="1">
         <v>2025</v>
       </c>
       <c r="I75" s="1" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="J75" s="1">
-        <v>9545000</v>
+        <v>3603000</v>
       </c>
       <c r="K75" s="1" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="76" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
-        <v>79</v>
+        <v>14</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="F76" s="1">
-        <v>6213</v>
+        <v>18678.36</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>210</v>
+        <v>184</v>
       </c>
       <c r="H76" s="1">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="I76" s="1" t="s">
-        <v>211</v>
+        <v>185</v>
       </c>
       <c r="J76" s="1">
-        <v>3603000</v>
+        <v>57124000</v>
       </c>
       <c r="K76" s="1" t="s">
-        <v>212</v>
+        <v>186</v>
       </c>
     </row>
     <row r="77" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
-        <v>14</v>
+        <v>96</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="F77" s="1">
-        <v>18678.36</v>
+        <v>18430.97</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="H77" s="1">
         <v>2022</v>
       </c>
       <c r="I77" s="1" t="s">
-        <v>191</v>
+        <v>202</v>
       </c>
       <c r="J77" s="1">
-        <v>57124000</v>
+        <v>7913000</v>
       </c>
       <c r="K77" s="1" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
     </row>
     <row r="78" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
-        <v>98</v>
+        <v>47</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>300</v>
+        <v>291</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="F78" s="1">
-        <v>18430.97</v>
+        <v>18982.099999999999</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="H78" s="1">
         <v>2022</v>
       </c>
       <c r="I78" s="1" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="J78" s="1">
-        <v>7913000</v>
+        <v>11549000</v>
       </c>
       <c r="K78" s="1" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
     </row>
     <row r="79" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="F79" s="1">
-        <v>18982.099999999999</v>
+        <v>29201.94</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>207</v>
+        <v>184</v>
       </c>
       <c r="H79" s="1">
         <v>2022</v>
       </c>
       <c r="I79" s="1" t="s">
-        <v>208</v>
+        <v>185</v>
       </c>
       <c r="J79" s="1">
-        <v>11549000</v>
+        <v>16206000</v>
       </c>
       <c r="K79" s="1" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
     </row>
     <row r="80" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="F80" s="1">
-        <v>29201.94</v>
+        <v>2226.4699999999998</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="H80" s="1">
         <v>2022</v>
       </c>
       <c r="I80" s="1" t="s">
-        <v>191</v>
+        <v>202</v>
       </c>
       <c r="J80" s="1">
-        <v>16206000</v>
+        <v>2571000</v>
       </c>
       <c r="K80" s="1" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
     </row>
     <row r="81" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>303</v>
+        <v>294</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E81" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="F81" s="1">
+        <v>19172</v>
+      </c>
+      <c r="G81" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="H81" s="1">
+        <v>2025</v>
+      </c>
+      <c r="I81" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="J81" s="1">
+        <v>257635000</v>
+      </c>
+      <c r="K81" s="1" t="s">
         <v>206</v>
-      </c>
-      <c r="F81" s="1">
-        <v>2226.4699999999998</v>
-      </c>
-      <c r="G81" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="H81" s="1">
-        <v>2022</v>
-      </c>
-      <c r="I81" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="J81" s="1">
-        <v>2571000</v>
-      </c>
-      <c r="K81" s="1" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="82" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
-        <v>80</v>
+        <v>207</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>304</v>
+        <v>295</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="F82" s="1">
-        <v>19172</v>
+        <v>21544</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>210</v>
+        <v>184</v>
       </c>
       <c r="H82" s="1">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="I82" s="1" t="s">
-        <v>211</v>
+        <v>185</v>
       </c>
       <c r="J82" s="1">
-        <v>257635000</v>
+        <v>0</v>
       </c>
       <c r="K82" s="1" t="s">
-        <v>212</v>
+        <v>186</v>
       </c>
     </row>
     <row r="83" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
-        <v>213</v>
+        <v>92</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="F83" s="1">
-        <v>21544</v>
+        <v>22803.78</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H83" s="1">
-        <v>2026</v>
+        <v>2022</v>
       </c>
       <c r="I83" s="1" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="J83" s="1">
-        <v>0</v>
+        <v>17302000</v>
       </c>
       <c r="K83" s="1" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
     </row>
     <row r="84" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
-        <v>94</v>
+        <v>50</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>306</v>
+        <v>297</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="F84" s="1">
-        <v>22803.78</v>
+        <v>14455.42</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H84" s="1">
         <v>2022</v>
       </c>
       <c r="I84" s="1" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="J84" s="1">
-        <v>17302000</v>
+        <v>6861000</v>
       </c>
       <c r="K84" s="1" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
     </row>
     <row r="85" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="1" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="F85" s="1">
-        <v>14455.42</v>
-      </c>
+        <v>199</v>
+      </c>
+      <c r="F85" s="1"/>
       <c r="G85" s="1" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H85" s="1">
-        <v>2022</v>
+        <v>2025</v>
       </c>
       <c r="I85" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="J85" s="1">
-        <v>6861000</v>
-      </c>
+        <v>185</v>
+      </c>
+      <c r="J85" s="1"/>
       <c r="K85" s="1" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
     </row>
     <row r="86" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="F86" s="1"/>
+        <v>199</v>
+      </c>
+      <c r="F86" s="1">
+        <v>842.82</v>
+      </c>
       <c r="G86" s="1" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H86" s="1">
         <v>2025</v>
       </c>
       <c r="I86" s="1" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="J86" s="1"/>
       <c r="K86" s="1" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
     </row>
     <row r="87" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="1" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>309</v>
+        <v>300</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>214</v>
+        <v>203</v>
       </c>
       <c r="F87" s="1">
-        <v>842.82</v>
+        <v>18060</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>190</v>
+        <v>204</v>
       </c>
       <c r="H87" s="1">
         <v>2025</v>
       </c>
       <c r="I87" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="J87" s="1"/>
+        <v>205</v>
+      </c>
+      <c r="J87" s="1">
+        <v>15213000</v>
+      </c>
       <c r="K87" s="1" t="s">
-        <v>192</v>
+        <v>206</v>
       </c>
     </row>
     <row r="88" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
-        <v>81</v>
+        <v>51</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>310</v>
+        <v>301</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="F88" s="1">
-        <v>18060</v>
+        <v>6441.67</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>210</v>
+        <v>184</v>
       </c>
       <c r="H88" s="1">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="I88" s="1" t="s">
-        <v>211</v>
+        <v>185</v>
       </c>
       <c r="J88" s="1">
-        <v>15213000</v>
+        <v>3636000</v>
       </c>
       <c r="K88" s="1" t="s">
-        <v>212</v>
+        <v>186</v>
       </c>
     </row>
     <row r="89" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>311</v>
+        <v>302</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="F89" s="1">
-        <v>6441.67</v>
+        <v>2531.13</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="H89" s="1">
         <v>2022</v>
       </c>
       <c r="I89" s="1" t="s">
-        <v>191</v>
+        <v>202</v>
       </c>
       <c r="J89" s="1">
-        <v>3636000</v>
+        <v>2303000</v>
       </c>
       <c r="K89" s="1" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
     </row>
     <row r="90" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>312</v>
+        <v>303</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="F90" s="1">
-        <v>2531.13</v>
+        <v>11946.16</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>207</v>
+        <v>184</v>
       </c>
       <c r="H90" s="1">
         <v>2022</v>
       </c>
       <c r="I90" s="1" t="s">
-        <v>208</v>
+        <v>185</v>
       </c>
       <c r="J90" s="1">
-        <v>2303000</v>
+        <v>7323000</v>
       </c>
       <c r="K90" s="1" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
     </row>
     <row r="91" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="1" t="s">
-        <v>53</v>
+        <v>3</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>313</v>
+        <v>304</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="F91" s="1">
-        <v>11946.16</v>
+        <v>10667.98</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="H91" s="1">
         <v>2022</v>
       </c>
       <c r="I91" s="1" t="s">
-        <v>191</v>
+        <v>202</v>
       </c>
       <c r="J91" s="1">
-        <v>7323000</v>
+        <v>34838000</v>
       </c>
       <c r="K91" s="1" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
     </row>
     <row r="92" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
-        <v>3</v>
+        <v>80</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>314</v>
+        <v>305</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E92" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="F92" s="1">
+        <v>9625</v>
+      </c>
+      <c r="G92" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="H92" s="1">
+        <v>2025</v>
+      </c>
+      <c r="I92" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="J92" s="1">
+        <v>4427000</v>
+      </c>
+      <c r="K92" s="1" t="s">
         <v>206</v>
-      </c>
-      <c r="F92" s="1">
-        <v>10667.98</v>
-      </c>
-      <c r="G92" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="H92" s="1">
-        <v>2022</v>
-      </c>
-      <c r="I92" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="J92" s="1">
-        <v>34838000</v>
-      </c>
-      <c r="K92" s="1" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="93" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="1" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>315</v>
+        <v>306</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="F93" s="1">
-        <v>9625</v>
+        <v>2065.86</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>210</v>
+        <v>184</v>
       </c>
       <c r="H93" s="1">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="I93" s="1" t="s">
-        <v>211</v>
+        <v>185</v>
       </c>
       <c r="J93" s="1">
-        <v>4427000</v>
+        <v>2090000</v>
       </c>
       <c r="K93" s="1" t="s">
-        <v>212</v>
+        <v>186</v>
       </c>
     </row>
     <row r="94" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
-        <v>97</v>
+        <v>81</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E94" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="F94" s="1">
+        <v>27009</v>
+      </c>
+      <c r="G94" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="H94" s="1">
+        <v>2025</v>
+      </c>
+      <c r="I94" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="F94" s="1">
-        <v>2065.86</v>
-      </c>
-      <c r="G94" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="H94" s="1">
-        <v>2022</v>
-      </c>
-      <c r="I94" s="1" t="s">
-        <v>191</v>
-      </c>
       <c r="J94" s="1">
-        <v>2090000</v>
+        <v>5740000</v>
       </c>
       <c r="K94" s="1" t="s">
-        <v>192</v>
+        <v>206</v>
       </c>
     </row>
     <row r="95" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>317</v>
+        <v>308</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="F95" s="1">
-        <v>27009</v>
+        <v>4206</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="H95" s="1">
         <v>2025</v>
       </c>
       <c r="I95" s="1" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="J95" s="1">
-        <v>5740000</v>
+        <v>3875000</v>
       </c>
       <c r="K95" s="1" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="96" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="1" t="s">
-        <v>84</v>
+        <v>4</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>318</v>
+        <v>309</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="F96" s="1">
-        <v>4206</v>
+        <v>18168.73</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="H96" s="1">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="I96" s="1" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="J96" s="1">
-        <v>3875000</v>
+        <v>16715000</v>
       </c>
       <c r="K96" s="1" t="s">
-        <v>212</v>
+        <v>186</v>
       </c>
     </row>
     <row r="97" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>319</v>
+        <v>310</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="F97" s="1">
-        <v>18168.73</v>
+        <v>14254.94</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="H97" s="1">
         <v>2022</v>
       </c>
       <c r="I97" s="1" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="J97" s="1">
-        <v>16715000</v>
+        <v>8090000</v>
       </c>
       <c r="K97" s="1" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
     </row>
     <row r="98" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="1" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="F98" s="1">
-        <v>14254.94</v>
+        <v>10638.02</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="H98" s="1">
         <v>2022</v>
       </c>
       <c r="I98" s="1" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="J98" s="1">
-        <v>8090000</v>
+        <v>7577000</v>
       </c>
       <c r="K98" s="1" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
     </row>
     <row r="99" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="1" t="s">
-        <v>11</v>
+        <v>83</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>321</v>
+        <v>312</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E99" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="F99" s="1">
+        <v>16345</v>
+      </c>
+      <c r="G99" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="H99" s="1">
+        <v>2025</v>
+      </c>
+      <c r="I99" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="J99" s="1">
+        <v>81499000</v>
+      </c>
+      <c r="K99" s="1" t="s">
         <v>206</v>
-      </c>
-      <c r="F99" s="1">
-        <v>10638.02</v>
-      </c>
-      <c r="G99" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="H99" s="1">
-        <v>2022</v>
-      </c>
-      <c r="I99" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="J99" s="1">
-        <v>7577000</v>
-      </c>
-      <c r="K99" s="1" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="100" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="1" t="s">
-        <v>85</v>
+        <v>53</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>322</v>
+        <v>313</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="F100" s="1">
-        <v>16345</v>
+        <v>31069.8</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H100" s="1">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="I100" s="1" t="s">
-        <v>211</v>
+        <v>185</v>
       </c>
       <c r="J100" s="1">
-        <v>81499000</v>
+        <v>11421600</v>
       </c>
       <c r="K100" s="1" t="s">
-        <v>212</v>
+        <v>186</v>
       </c>
     </row>
     <row r="101" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="1" t="s">
-        <v>54</v>
+        <v>208</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>323</v>
+        <v>314</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E101" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="F101" s="1">
+        <v>2020</v>
+      </c>
+      <c r="G101" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="H101" s="1">
+        <v>2025</v>
+      </c>
+      <c r="I101" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="F101" s="1">
-        <v>31069.8</v>
-      </c>
-      <c r="G101" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="H101" s="1">
-        <v>2022</v>
-      </c>
-      <c r="I101" s="1" t="s">
-        <v>191</v>
-      </c>
       <c r="J101" s="1">
-        <v>11421600</v>
+        <v>0</v>
       </c>
       <c r="K101" s="1" t="s">
-        <v>192</v>
+        <v>206</v>
       </c>
     </row>
     <row r="102" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="1" t="s">
-        <v>215</v>
+        <v>84</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="F102" s="1">
-        <v>2020</v>
+        <v>8242</v>
       </c>
       <c r="G102" s="1" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="H102" s="1">
         <v>2025</v>
       </c>
       <c r="I102" s="1" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="J102" s="1">
-        <v>0</v>
+        <v>5485000</v>
       </c>
       <c r="K102" s="1" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="103" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>325</v>
+        <v>316</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="F103" s="1">
-        <v>8242</v>
+        <v>8235</v>
       </c>
       <c r="G103" s="1" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="H103" s="1">
         <v>2025</v>
       </c>
       <c r="I103" s="1" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="J103" s="1">
-        <v>5485000</v>
+        <v>6940000</v>
       </c>
       <c r="K103" s="1" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="104" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>326</v>
+        <v>317</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="F104" s="1">
-        <v>8235</v>
+        <v>11262</v>
       </c>
       <c r="G104" s="1" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="H104" s="1">
         <v>2025</v>
       </c>
       <c r="I104" s="1" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="J104" s="1">
-        <v>6940000</v>
+        <v>5787000</v>
       </c>
       <c r="K104" s="1" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="105" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="1" t="s">
-        <v>55</v>
+        <v>87</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>327</v>
+        <v>318</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E105" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="F105" s="1">
+        <v>14822</v>
+      </c>
+      <c r="G105" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="H105" s="1">
+        <v>2025</v>
+      </c>
+      <c r="I105" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="F105" s="1">
-        <v>16516</v>
-      </c>
-      <c r="G105" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="H105" s="1">
-        <v>2022</v>
-      </c>
-      <c r="I105" s="1" t="s">
-        <v>191</v>
-      </c>
       <c r="J105" s="1">
-        <v>8118000</v>
+        <v>15653000</v>
       </c>
       <c r="K105" s="1" t="s">
-        <v>192</v>
+        <v>206</v>
       </c>
     </row>
     <row r="106" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="1" t="s">
-        <v>88</v>
+        <v>13</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>92</v>
+        <v>209</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>102</v>
+        <v>320</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>209</v>
+        <v>13</v>
       </c>
       <c r="F106" s="1">
-        <v>11262</v>
+        <v>3357.96</v>
       </c>
       <c r="G106" s="1" t="s">
         <v>210</v>
       </c>
       <c r="H106" s="1">
-        <v>2025</v>
+        <v>2021</v>
       </c>
       <c r="I106" s="1" t="s">
         <v>211</v>
       </c>
       <c r="J106" s="1">
-        <v>5787000</v>
+        <v>6542000</v>
       </c>
       <c r="K106" s="1" t="s">
         <v>212</v>
@@ -5105,109 +5082,76 @@
     </row>
     <row r="107" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="1" t="s">
-        <v>89</v>
+        <v>322</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>92</v>
+        <v>125</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>209</v>
+        <v>322</v>
       </c>
       <c r="F107" s="1">
-        <v>14822</v>
+        <v>19209</v>
       </c>
       <c r="G107" s="1" t="s">
-        <v>210</v>
+        <v>323</v>
       </c>
       <c r="H107" s="1">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="I107" s="1" t="s">
-        <v>211</v>
+        <v>324</v>
       </c>
       <c r="J107" s="1">
-        <v>15653000</v>
+        <v>2360146.87</v>
       </c>
       <c r="K107" s="1" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="108" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A108" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B108" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="C108" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="D108" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E108" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F108" s="1">
-        <v>3357.96</v>
-      </c>
-      <c r="G108" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="H108" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I108" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="J108" s="1">
-        <v>6542000</v>
-      </c>
-      <c r="K108" s="1" t="s">
-        <v>219</v>
+        <v>325</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:K106" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <hyperlinks>
-    <hyperlink ref="K5" r:id="rId1" xr:uid="{9B4BA460-A56F-4E84-B40E-6E923AB0D0A0}"/>
-    <hyperlink ref="K6" r:id="rId2" xr:uid="{6559BD48-F420-4775-BDA2-AFD3833D04E1}"/>
-    <hyperlink ref="K29" r:id="rId3" xr:uid="{180BCD79-9E3C-417A-B053-D54A2AA8BF31}"/>
-    <hyperlink ref="K30" r:id="rId4" xr:uid="{B18BAED7-717B-439B-B8AD-95D00593E055}"/>
-    <hyperlink ref="K31" r:id="rId5" xr:uid="{6C2146F8-8297-4991-BA36-D44E1A302FFB}"/>
-    <hyperlink ref="K32" r:id="rId6" xr:uid="{7E467724-B1C8-4BD2-AF65-E5B3B5408ACE}"/>
-    <hyperlink ref="K33" r:id="rId7" xr:uid="{25837FD0-BF95-4128-A3D3-F68E1A7B85F3}"/>
-    <hyperlink ref="K34" r:id="rId8" display="https://educacao.sme.prefeitura.sp.gov.br/noticias/chamamento-publico-gestao-12-ceus/" xr:uid="{B4B7A37B-D630-4176-A27E-B6F4ECACD7A3}"/>
-    <hyperlink ref="K43" r:id="rId9" xr:uid="{4FBB7EDE-7314-4AD4-AE45-2E829F152DD1}"/>
-    <hyperlink ref="K75" r:id="rId10" xr:uid="{CEE0A66D-F568-4A72-BF88-4AAD5A49F397}"/>
-    <hyperlink ref="K76" r:id="rId11" display="https://educacao.sme.prefeitura.sp.gov.br/noticias/chamamento-publico-gestao-12-ceus/" xr:uid="{B98D2180-A195-4201-8E1C-5FFF5BFE3A41}"/>
-    <hyperlink ref="K77" r:id="rId12" display="https://educacao.sme.prefeitura.sp.gov.br/noticias/chamamento-publico-gestao-12-ceus/" xr:uid="{60B25D3D-224E-4D11-8FB6-36FE93C6B6A6}"/>
-    <hyperlink ref="K78" r:id="rId13" display="https://educacao.sme.prefeitura.sp.gov.br/noticias/chamamento-publico-gestao-12-ceus/" xr:uid="{35CA9D5C-2640-4067-8D64-9775FFAA3271}"/>
-    <hyperlink ref="K79" r:id="rId14" display="https://educacao.sme.prefeitura.sp.gov.br/noticias/chamamento-publico-gestao-12-ceus/" xr:uid="{EBB673BB-E00F-49F9-8E9B-46D00FD45992}"/>
-    <hyperlink ref="K80" r:id="rId15" display="https://educacao.sme.prefeitura.sp.gov.br/noticias/chamamento-publico-gestao-12-ceus/" xr:uid="{B1B81F61-67D1-49EE-9ACC-6BAAA209C5FA}"/>
-    <hyperlink ref="K81" r:id="rId16" display="https://educacao.sme.prefeitura.sp.gov.br/noticias/chamamento-publico-gestao-12-ceus/" xr:uid="{B51D5BCD-83F9-4733-AA18-F99D842E80DD}"/>
-    <hyperlink ref="K82" r:id="rId17" display="https://educacao.sme.prefeitura.sp.gov.br/noticias/chamamento-publico-gestao-12-ceus/" xr:uid="{0CB17215-2040-48B1-BD5B-2D91C7FE162F}"/>
-    <hyperlink ref="K83" r:id="rId18" display="https://educacao.sme.prefeitura.sp.gov.br/noticias/chamamento-publico-gestao-12-ceus/" xr:uid="{5469FEA8-D895-4ADE-BB16-17B4FB43DFC6}"/>
-    <hyperlink ref="K84" r:id="rId19" display="https://educacao.sme.prefeitura.sp.gov.br/noticias/chamamento-publico-gestao-12-ceus/" xr:uid="{66733EC7-24B8-4C12-9F41-0B3B9F0AB66E}"/>
-    <hyperlink ref="K85" r:id="rId20" display="https://educacao.sme.prefeitura.sp.gov.br/noticias/chamamento-publico-gestao-12-ceus/" xr:uid="{C4A22A8E-32A9-4E73-A9AD-169C13323991}"/>
-    <hyperlink ref="K86" r:id="rId21" display="https://educacao.sme.prefeitura.sp.gov.br/noticias/chamamento-publico-gestao-12-ceus/" xr:uid="{8E07F162-0703-49FC-BF84-ADAA9A03E99A}"/>
-    <hyperlink ref="K88" r:id="rId22" xr:uid="{D909D141-53B9-4C0F-8F7E-1A9AF8AC2220}"/>
-    <hyperlink ref="K93" r:id="rId23" xr:uid="{18ED7079-02A4-4274-BD57-E5E0828D4677}"/>
-    <hyperlink ref="K95" r:id="rId24" xr:uid="{BB47E403-A174-4A5F-8FF9-DD4DE360E312}"/>
-    <hyperlink ref="K96" r:id="rId25" xr:uid="{27F347E6-AD5C-4286-BE93-A4B4932712C0}"/>
-    <hyperlink ref="K100" r:id="rId26" xr:uid="{AC398316-00F6-455E-A53D-C84D66380B6A}"/>
-    <hyperlink ref="K102" r:id="rId27" xr:uid="{D5B11967-6974-4B11-BCD0-090972F1E2E3}"/>
-    <hyperlink ref="K103" r:id="rId28" xr:uid="{4A78D1CC-00A2-4BEC-88A3-2475612EBF26}"/>
-    <hyperlink ref="K104" r:id="rId29" xr:uid="{447CC212-8EEE-4621-B932-EC7ECDA0895B}"/>
-    <hyperlink ref="K106" r:id="rId30" xr:uid="{34F84606-8190-44E0-A42C-694E8D78CAB7}"/>
-    <hyperlink ref="K107" r:id="rId31" xr:uid="{6BA23300-3D07-461B-AB4E-93779D248A41}"/>
-    <hyperlink ref="K4" r:id="rId32" xr:uid="{B468E687-6491-4A8B-AA81-038FE9A3A673}"/>
+    <hyperlink ref="K4" r:id="rId1" xr:uid="{9B4BA460-A56F-4E84-B40E-6E923AB0D0A0}"/>
+    <hyperlink ref="K5" r:id="rId2" xr:uid="{6559BD48-F420-4775-BDA2-AFD3833D04E1}"/>
+    <hyperlink ref="K28" r:id="rId3" xr:uid="{180BCD79-9E3C-417A-B053-D54A2AA8BF31}"/>
+    <hyperlink ref="K29" r:id="rId4" xr:uid="{B18BAED7-717B-439B-B8AD-95D00593E055}"/>
+    <hyperlink ref="K30" r:id="rId5" xr:uid="{6C2146F8-8297-4991-BA36-D44E1A302FFB}"/>
+    <hyperlink ref="K31" r:id="rId6" xr:uid="{7E467724-B1C8-4BD2-AF65-E5B3B5408ACE}"/>
+    <hyperlink ref="K32" r:id="rId7" xr:uid="{25837FD0-BF95-4128-A3D3-F68E1A7B85F3}"/>
+    <hyperlink ref="K33" r:id="rId8" display="https://educacao.sme.prefeitura.sp.gov.br/noticias/chamamento-publico-gestao-12-ceus/" xr:uid="{B4B7A37B-D630-4176-A27E-B6F4ECACD7A3}"/>
+    <hyperlink ref="K42" r:id="rId9" xr:uid="{4FBB7EDE-7314-4AD4-AE45-2E829F152DD1}"/>
+    <hyperlink ref="K74" r:id="rId10" xr:uid="{CEE0A66D-F568-4A72-BF88-4AAD5A49F397}"/>
+    <hyperlink ref="K75" r:id="rId11" display="https://educacao.sme.prefeitura.sp.gov.br/noticias/chamamento-publico-gestao-12-ceus/" xr:uid="{B98D2180-A195-4201-8E1C-5FFF5BFE3A41}"/>
+    <hyperlink ref="K76" r:id="rId12" display="https://educacao.sme.prefeitura.sp.gov.br/noticias/chamamento-publico-gestao-12-ceus/" xr:uid="{60B25D3D-224E-4D11-8FB6-36FE93C6B6A6}"/>
+    <hyperlink ref="K77" r:id="rId13" display="https://educacao.sme.prefeitura.sp.gov.br/noticias/chamamento-publico-gestao-12-ceus/" xr:uid="{35CA9D5C-2640-4067-8D64-9775FFAA3271}"/>
+    <hyperlink ref="K78" r:id="rId14" display="https://educacao.sme.prefeitura.sp.gov.br/noticias/chamamento-publico-gestao-12-ceus/" xr:uid="{EBB673BB-E00F-49F9-8E9B-46D00FD45992}"/>
+    <hyperlink ref="K79" r:id="rId15" display="https://educacao.sme.prefeitura.sp.gov.br/noticias/chamamento-publico-gestao-12-ceus/" xr:uid="{B1B81F61-67D1-49EE-9ACC-6BAAA209C5FA}"/>
+    <hyperlink ref="K80" r:id="rId16" display="https://educacao.sme.prefeitura.sp.gov.br/noticias/chamamento-publico-gestao-12-ceus/" xr:uid="{B51D5BCD-83F9-4733-AA18-F99D842E80DD}"/>
+    <hyperlink ref="K81" r:id="rId17" display="https://educacao.sme.prefeitura.sp.gov.br/noticias/chamamento-publico-gestao-12-ceus/" xr:uid="{0CB17215-2040-48B1-BD5B-2D91C7FE162F}"/>
+    <hyperlink ref="K82" r:id="rId18" display="https://educacao.sme.prefeitura.sp.gov.br/noticias/chamamento-publico-gestao-12-ceus/" xr:uid="{5469FEA8-D895-4ADE-BB16-17B4FB43DFC6}"/>
+    <hyperlink ref="K83" r:id="rId19" display="https://educacao.sme.prefeitura.sp.gov.br/noticias/chamamento-publico-gestao-12-ceus/" xr:uid="{66733EC7-24B8-4C12-9F41-0B3B9F0AB66E}"/>
+    <hyperlink ref="K84" r:id="rId20" display="https://educacao.sme.prefeitura.sp.gov.br/noticias/chamamento-publico-gestao-12-ceus/" xr:uid="{C4A22A8E-32A9-4E73-A9AD-169C13323991}"/>
+    <hyperlink ref="K85" r:id="rId21" display="https://educacao.sme.prefeitura.sp.gov.br/noticias/chamamento-publico-gestao-12-ceus/" xr:uid="{8E07F162-0703-49FC-BF84-ADAA9A03E99A}"/>
+    <hyperlink ref="K87" r:id="rId22" xr:uid="{D909D141-53B9-4C0F-8F7E-1A9AF8AC2220}"/>
+    <hyperlink ref="K92" r:id="rId23" xr:uid="{18ED7079-02A4-4274-BD57-E5E0828D4677}"/>
+    <hyperlink ref="K94" r:id="rId24" xr:uid="{BB47E403-A174-4A5F-8FF9-DD4DE360E312}"/>
+    <hyperlink ref="K95" r:id="rId25" xr:uid="{27F347E6-AD5C-4286-BE93-A4B4932712C0}"/>
+    <hyperlink ref="K99" r:id="rId26" xr:uid="{AC398316-00F6-455E-A53D-C84D66380B6A}"/>
+    <hyperlink ref="K101" r:id="rId27" xr:uid="{D5B11967-6974-4B11-BCD0-090972F1E2E3}"/>
+    <hyperlink ref="K102" r:id="rId28" xr:uid="{4A78D1CC-00A2-4BEC-88A3-2475612EBF26}"/>
+    <hyperlink ref="K103" r:id="rId29" xr:uid="{447CC212-8EEE-4621-B932-EC7ECDA0895B}"/>
+    <hyperlink ref="K104" r:id="rId30" xr:uid="{34F84606-8190-44E0-A42C-694E8D78CAB7}"/>
+    <hyperlink ref="K105" r:id="rId31" xr:uid="{6BA23300-3D07-461B-AB4E-93779D248A41}"/>
+    <hyperlink ref="K107" r:id="rId32" xr:uid="{6FF6A4ED-B033-4A2E-958D-DE17A625775E}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId33"/>
 </worksheet>
 </file>